--- a/database/event/official_evp_lists.xlsx
+++ b/database/event/official_evp_lists.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q325"/>
+  <dimension ref="A1:Q326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,6 @@
           <t>fifflaren</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -587,19 +583,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -618,19 +601,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -649,19 +619,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -680,19 +637,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -731,15 +675,6 @@
           <t>scream</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -758,19 +693,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -789,19 +711,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -820,19 +729,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -851,19 +747,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -882,19 +765,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -913,19 +783,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -944,19 +801,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -975,19 +819,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1006,19 +837,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1037,19 +855,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1068,19 +873,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1099,19 +891,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1130,19 +909,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1161,19 +927,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1192,19 +945,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1223,19 +963,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1254,19 +981,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1300,16 +1014,6 @@
           <t>dazed</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1338,17 +1042,6 @@
           <t>get-right</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1377,17 +1070,6 @@
           <t>byali</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1436,13 +1118,6 @@
           <t>snax</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1481,15 +1156,6 @@
           <t>xizt</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1518,17 +1184,6 @@
           <t>get-right</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1557,17 +1212,6 @@
           <t>n0thing</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1591,18 +1235,6 @@
           <t>apex</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1631,17 +1263,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1675,16 +1296,6 @@
           <t>get-right</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1713,17 +1324,6 @@
           <t>guardian</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1752,17 +1352,6 @@
           <t>shox</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1791,17 +1380,6 @@
           <t>s1mple</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1835,16 +1413,6 @@
           <t>guardian</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1873,17 +1441,6 @@
           <t>swag</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1907,18 +1464,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1942,18 +1487,6 @@
           <t>jw</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1982,17 +1515,6 @@
           <t>kioshima</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2016,18 +1538,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2051,18 +1561,6 @@
           <t>shox</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2086,18 +1584,6 @@
           <t>kennys</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2121,18 +1607,6 @@
           <t>nbk</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2161,17 +1635,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2195,18 +1658,6 @@
           <t>shox</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2230,18 +1681,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2275,16 +1714,6 @@
           <t>snax</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2313,17 +1742,6 @@
           <t>get-right</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2352,17 +1770,6 @@
           <t>cajunb</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2391,17 +1798,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2425,18 +1821,6 @@
           <t>krimz</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2460,18 +1844,6 @@
           <t>krimz</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2505,16 +1877,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2543,17 +1905,6 @@
           <t>happy</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2582,17 +1933,6 @@
           <t>shox</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2626,16 +1966,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2664,17 +1994,6 @@
           <t>happy</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2708,16 +2027,6 @@
           <t>apex</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2741,18 +2050,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2781,17 +2078,6 @@
           <t>pashabiceps</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2820,17 +2106,6 @@
           <t>krimz</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2854,18 +2129,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2889,18 +2152,6 @@
           <t>flamie</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2924,18 +2175,6 @@
           <t>flamie</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2964,17 +2203,6 @@
           <t>snax</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3008,16 +2236,6 @@
           <t>jw</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3036,19 +2254,6 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3077,17 +2282,6 @@
           <t>kioshima</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3111,18 +2305,6 @@
           <t>pashabiceps</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3146,18 +2328,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3181,18 +2351,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3216,18 +2374,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3256,17 +2402,6 @@
           <t>snax</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3310,14 +2445,6 @@
           <t>hen1</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3366,13 +2493,6 @@
           <t>fer</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3421,13 +2541,6 @@
           <t>flusha</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3451,18 +2564,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3506,14 +2607,6 @@
           <t>kjaerbye</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3557,14 +2650,6 @@
           <t>fer</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3608,14 +2693,6 @@
           <t>edward</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3664,13 +2741,6 @@
           <t>fallen</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3719,13 +2789,6 @@
           <t>elige</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3769,14 +2832,6 @@
           <t>f0rest</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3825,13 +2880,6 @@
           <t>jw</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3860,17 +2908,6 @@
           <t>lucas1</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3914,14 +2951,6 @@
           <t>jks</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3960,15 +2989,6 @@
           <t>taz</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4012,14 +3032,6 @@
           <t>fnx</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4068,13 +3080,6 @@
           <t>neo</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4118,14 +3123,6 @@
           <t>magisk</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4169,14 +3166,6 @@
           <t>edward</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4225,13 +3214,6 @@
           <t>neo</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4270,15 +3252,6 @@
           <t>fnx</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4327,13 +3300,6 @@
           <t>pyth</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4372,15 +3338,6 @@
           <t>stewie2k</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4429,13 +3386,6 @@
           <t>maikelele</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4484,13 +3434,6 @@
           <t>naf</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4544,12 +3487,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4593,14 +3530,6 @@
           <t>rubino</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4644,14 +3573,6 @@
           <t>fer</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4700,13 +3621,6 @@
           <t>pashabiceps</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4755,13 +3669,6 @@
           <t>nbk</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4800,15 +3707,6 @@
           <t>nbk</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -4857,13 +3755,6 @@
           <t>mou</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4917,12 +3808,6 @@
           <t>apex</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4961,15 +3846,6 @@
           <t>felps</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5003,16 +3879,6 @@
           <t>cajunb</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5056,14 +3922,6 @@
           <t>skadoodle</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5107,14 +3965,6 @@
           <t>oskar</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5168,12 +4018,6 @@
           <t>stewie2k</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5227,12 +4071,6 @@
           <t>elige</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5286,12 +4124,6 @@
           <t>allu</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5345,12 +4177,6 @@
           <t>hobbit</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5399,13 +4225,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5444,15 +4263,6 @@
           <t>valde</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5496,14 +4306,6 @@
           <t>rain</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5557,12 +4359,6 @@
           <t>boltz</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5611,13 +4407,6 @@
           <t>fallen</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5671,12 +4460,6 @@
           <t>get-right</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5730,12 +4513,6 @@
           <t>xyp9x</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5789,12 +4566,6 @@
           <t>xyp9x</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5823,17 +4594,6 @@
           <t>elige</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5892,11 +4652,6 @@
           <t>taco</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6023,14 +4778,6 @@
           <t>pashabiceps</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6069,15 +4816,6 @@
           <t>autimatic</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6106,17 +4844,6 @@
           <t>pashabiceps</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6180,10 +4907,6 @@
           <t>stewie2k</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6247,10 +4970,6 @@
           <t>autimatic</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6294,14 +5013,6 @@
           <t>olofmeister</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6355,12 +5066,6 @@
           <t>naf</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6419,11 +5124,6 @@
           <t>gla1ve</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6477,12 +5177,6 @@
           <t>valde</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6541,11 +5235,6 @@
           <t>nex</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6589,14 +5278,6 @@
           <t>bondik</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6620,18 +5301,6 @@
           <t>nexa</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6660,17 +5329,6 @@
           <t>mixwell</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6729,11 +5387,6 @@
           <t>twistzz</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6772,15 +5425,6 @@
           <t>gla1ve</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6854,8 +5498,6 @@
           <t>chrisj</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6909,12 +5551,6 @@
           <t>adren</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6963,13 +5599,6 @@
           <t>styko</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7013,14 +5642,6 @@
           <t>magisk</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7074,12 +5695,6 @@
           <t>rain</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7143,10 +5758,6 @@
           <t>xyp9x</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7185,15 +5796,6 @@
           <t>tarik</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7237,14 +5839,6 @@
           <t>gla1ve</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7293,13 +5887,6 @@
           <t>rain</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7358,11 +5945,6 @@
           <t>edward</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7396,16 +5978,6 @@
           <t>lekr0</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7454,13 +6026,6 @@
           <t>chrisj</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7509,13 +6074,6 @@
           <t>flamie</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7549,16 +6107,6 @@
           <t>bntet</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7617,11 +6165,6 @@
           <t>xseven</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7685,10 +6228,6 @@
           <t>tonyblack</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7752,10 +6291,6 @@
           <t>xyp9x</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7809,12 +6344,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7863,13 +6392,6 @@
           <t>ethan</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7928,11 +6450,6 @@
           <t>magisk</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7981,13 +6498,6 @@
           <t>k0nfig</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8046,11 +6556,6 @@
           <t>naf</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8084,16 +6589,6 @@
           <t>s1mple</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8152,11 +6647,6 @@
           <t>brollan</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8215,11 +6705,6 @@
           <t>twist</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8278,11 +6763,6 @@
           <t>stewie2k</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8331,13 +6811,6 @@
           <t>twistzz</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8366,17 +6839,6 @@
           <t>fer</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8425,13 +6887,6 @@
           <t>stewie2k</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8465,16 +6920,6 @@
           <t>adren</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8518,14 +6963,6 @@
           <t>sergej</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8584,11 +7021,6 @@
           <t>rain</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -8637,13 +7069,6 @@
           <t>kscerato</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8707,10 +7132,6 @@
           <t>buster</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8769,11 +7190,6 @@
           <t>amanek</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8817,14 +7233,6 @@
           <t>elige</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8883,11 +7291,6 @@
           <t>brollan</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8941,12 +7344,6 @@
           <t>twistzz</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9010,10 +7407,6 @@
           <t>sergej</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9072,11 +7465,6 @@
           <t>magisk</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9105,17 +7493,6 @@
           <t>sergej</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9134,19 +7511,6 @@
       <c r="D184" t="n">
         <v>1</v>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9210,10 +7574,6 @@
           <t>frozen</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9262,13 +7622,6 @@
           <t>f0rest</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9292,18 +7645,6 @@
           <t>ropz</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9357,12 +7698,6 @@
           <t>jkaem</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9421,11 +7756,6 @@
           <t>hunter</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9469,14 +7799,6 @@
           <t>elige</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9540,10 +7862,6 @@
           <t>flamie</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9592,13 +7910,6 @@
           <t>stewie2k</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9652,12 +7963,6 @@
           <t>flusha</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9721,10 +8026,6 @@
           <t>niko</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9763,15 +8064,6 @@
           <t>rpk</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9820,13 +8112,6 @@
           <t>jackz</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9875,13 +8160,6 @@
           <t>boombl4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9930,13 +8208,6 @@
           <t>poizon</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9985,13 +8256,6 @@
           <t>perfecto</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -10050,11 +8314,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10118,10 +8377,6 @@
           <t>nafany</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10195,8 +8450,6 @@
           <t>frozen</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -10245,13 +8498,6 @@
           <t>cerq</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -10290,15 +8536,6 @@
           <t>niko</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -10347,13 +8584,6 @@
           <t>fallen</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -10412,11 +8642,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10480,10 +8705,6 @@
           <t>koosta</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -10547,10 +8768,6 @@
           <t>xantares</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10599,13 +8816,6 @@
           <t>kscerato</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10664,11 +8874,6 @@
           <t>tabsen</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10717,13 +8922,6 @@
           <t>bntet</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10787,10 +8985,6 @@
           <t>teses</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10834,14 +9028,6 @@
           <t>cerq</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -10895,12 +9081,6 @@
           <t>tabsen</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -10949,13 +9129,6 @@
           <t>issaa</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11019,10 +9192,6 @@
           <t>gratisfaction</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -11081,11 +9250,6 @@
           <t>hunter</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -11134,13 +9298,6 @@
           <t>gratisfaction</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -11194,12 +9351,6 @@
           <t>nawwk</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -11263,10 +9414,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -11330,10 +9477,6 @@
           <t>rpk</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -11382,13 +9525,6 @@
           <t>dupreeh</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -11447,11 +9583,6 @@
           <t>mir</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -11530,7 +9661,6 @@
           <t>stavn</t>
         </is>
       </c>
-      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -11609,7 +9739,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -11678,9 +9807,6 @@
           <t>yekindar</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -11729,13 +9855,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -11779,14 +9898,6 @@
           <t>blamef</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -11835,13 +9946,6 @@
           <t>b1t</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -11895,12 +9999,6 @@
           <t>brollan</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -11964,10 +10062,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -12026,11 +10120,6 @@
           <t>sunpayus</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -12089,11 +10178,6 @@
           <t>rez</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -12137,14 +10221,6 @@
           <t>rez</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -12188,14 +10264,6 @@
           <t>ax1le</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -12254,11 +10322,6 @@
           <t>hobbit</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -12307,13 +10370,6 @@
           <t>nickelback</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -12382,9 +10438,6 @@
           <t>hobbit</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -12458,8 +10511,6 @@
           <t>ropz</t>
         </is>
       </c>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -12523,10 +10574,6 @@
           <t>rain</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -12585,11 +10632,6 @@
           <t>dycha</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -12653,10 +10695,6 @@
           <t>ropz</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -12793,12 +10831,6 @@
           <t>forester</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -12842,14 +10874,6 @@
           <t>degster</t>
         </is>
       </c>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -12893,14 +10917,6 @@
           <t>jabbi</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -12954,12 +10970,6 @@
           <t>yekindar</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -13023,10 +11033,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -13075,13 +11081,6 @@
           <t>cadian</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -13120,15 +11119,6 @@
           <t>twistzz</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -13197,9 +11187,6 @@
           <t>stavn</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -13263,10 +11250,6 @@
           <t>acor</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -13335,9 +11318,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -13386,13 +11366,6 @@
           <t>sunpayus</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
-      <c r="P254" t="inlineStr"/>
-      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -13446,12 +11419,6 @@
           <t>nertz</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -13515,10 +11482,6 @@
           <t>hobbit</t>
         </is>
       </c>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -13597,7 +11560,6 @@
           <t>xertion</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -13646,13 +11608,6 @@
           <t>electronic</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -13711,11 +11666,6 @@
           <t>twistzz</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -13754,15 +11704,6 @@
           <t>krasnal</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -13816,12 +11757,6 @@
           <t>jame</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
-      <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -13865,14 +11800,6 @@
           <t>stavn</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
-      <c r="O262" t="inlineStr"/>
-      <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -13911,15 +11838,6 @@
           <t>flamez</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
-      <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -13968,13 +11886,6 @@
           <t>flamez</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
-      <c r="O264" t="inlineStr"/>
-      <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -14038,10 +11949,6 @@
           <t>spinx</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -14095,12 +12002,6 @@
           <t>broky</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -14129,17 +12030,6 @@
           <t>art</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
-      <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -14208,9 +12098,6 @@
           <t>fl1t</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -14254,14 +12141,6 @@
           <t>frozen</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
-      <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -14305,14 +12184,6 @@
           <t>broky</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
-      <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -14366,12 +12237,6 @@
           <t>ewjerkz</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
-      <c r="O271" t="inlineStr"/>
-      <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -14420,13 +12285,6 @@
           <t>xertion</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
-      <c r="O272" t="inlineStr"/>
-      <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -14470,14 +12328,6 @@
           <t>spinx</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
-      <c r="O273" t="inlineStr"/>
-      <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -14531,12 +12381,6 @@
           <t>w0nderful</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
-      <c r="O274" t="inlineStr"/>
-      <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -14590,12 +12434,6 @@
           <t>torzsi</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
-      <c r="O275" t="inlineStr"/>
-      <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -14654,11 +12492,6 @@
           <t>woxic</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
-      <c r="O276" t="inlineStr"/>
-      <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -14697,15 +12530,6 @@
           <t>senzu</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
-      <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -14749,14 +12573,6 @@
           <t>flamez</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
-      <c r="O278" t="inlineStr"/>
-      <c r="P278" t="inlineStr"/>
-      <c r="Q278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -14805,13 +12621,6 @@
           <t>fl1t</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
-      <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -14855,14 +12664,6 @@
           <t>sh1ro</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
-      <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -14911,13 +12712,6 @@
           <t>malbsmd</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
-      <c r="O281" t="inlineStr"/>
-      <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -14961,14 +12755,6 @@
           <t>sh1ro</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -15007,15 +12793,6 @@
           <t>jl</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
-      <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -15054,15 +12831,6 @@
           <t>jimpphat</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
-      <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -15116,12 +12884,6 @@
           <t>910</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -15155,16 +12917,6 @@
           <t>sh1ro</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
-      <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -15198,16 +12950,6 @@
           <t>ropz</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
-      <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -15241,16 +12983,6 @@
           <t>yekindar</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
-      <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -15289,15 +13021,6 @@
           <t>xantares</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
-      <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -15331,16 +13054,6 @@
           <t>zywoo</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
-      <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -15379,15 +13092,6 @@
           <t>donk</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
-      <c r="O291" t="inlineStr"/>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -15426,15 +13130,6 @@
           <t>woxic</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
-      <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -15463,17 +13158,6 @@
           <t>n1ssim</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
-      <c r="O293" t="inlineStr"/>
-      <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -15512,15 +13196,6 @@
           <t>xantares</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
-      <c r="O294" t="inlineStr"/>
-      <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -15554,16 +13229,6 @@
           <t>teses</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr"/>
-      <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -15602,15 +13267,6 @@
           <t>910</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -15659,13 +13315,6 @@
           <t>torzsi</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
-      <c r="O297" t="inlineStr"/>
-      <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -15699,16 +13348,6 @@
           <t>senzu</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
-      <c r="O298" t="inlineStr"/>
-      <c r="P298" t="inlineStr"/>
-      <c r="Q298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -15762,12 +13401,6 @@
           <t>flamez</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
-      <c r="O299" t="inlineStr"/>
-      <c r="P299" t="inlineStr"/>
-      <c r="Q299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -15821,12 +13454,6 @@
           <t>yekindar</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
-      <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr"/>
-      <c r="Q300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -15895,9 +13522,6 @@
           <t>twistzz</t>
         </is>
       </c>
-      <c r="O301" t="inlineStr"/>
-      <c r="P301" t="inlineStr"/>
-      <c r="Q301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -15946,13 +13570,6 @@
           <t>xertion</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
-      <c r="O302" t="inlineStr"/>
-      <c r="P302" t="inlineStr"/>
-      <c r="Q302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -16001,13 +13618,6 @@
           <t>teses</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -16041,16 +13651,6 @@
           <t>staehr</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
-      <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
-      <c r="Q304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -16089,15 +13689,6 @@
           <t>saadzin</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr"/>
-      <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -16156,11 +13747,6 @@
           <t>zweih</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr"/>
-      <c r="O306" t="inlineStr"/>
-      <c r="P306" t="inlineStr"/>
-      <c r="Q306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -16219,11 +13805,6 @@
           <t>phzy</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -16282,11 +13863,6 @@
           <t>tn1r</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
-      <c r="O308" t="inlineStr"/>
-      <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -16315,17 +13891,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -16384,11 +13949,6 @@
           <t>yekindar</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
-      <c r="O310" t="inlineStr"/>
-      <c r="P310" t="inlineStr"/>
-      <c r="Q310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -16427,15 +13987,6 @@
           <t>makazze</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
-      <c r="O311" t="inlineStr"/>
-      <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -16484,13 +14035,6 @@
           <t>molodoy</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
-      <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -16539,13 +14083,6 @@
           <t>tn1r</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
-      <c r="O313" t="inlineStr"/>
-      <c r="P313" t="inlineStr"/>
-      <c r="Q313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -16594,13 +14131,6 @@
           <t>tauson</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
-      <c r="O314" t="inlineStr"/>
-      <c r="P314" t="inlineStr"/>
-      <c r="Q314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -16624,18 +14154,6 @@
           <t>nota</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
-      <c r="O315" t="inlineStr"/>
-      <c r="P315" t="inlineStr"/>
-      <c r="Q315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -16659,18 +14177,6 @@
           <t>torzsi</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
-      <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -16714,426 +14220,405 @@
           <t>wicadia</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
-      <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" t="n">
-        <v>8250</v>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>8249</t>
+        </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>BLAST Rivals 2026 Season 1</t>
+          <t>BLAST Open Porto 2026</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
+          <t>donk</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>7</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>sh1ro</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>xelex</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>m0nesy</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
           <t>zywoo</t>
         </is>
       </c>
-      <c r="D318" t="n">
-        <v>5</v>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>w0nderful</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>makazze</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>flamez</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>ropz</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
-      <c r="O318" t="inlineStr"/>
-      <c r="P318" t="inlineStr"/>
-      <c r="Q318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>tn1r</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>spinx</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>8261</v>
+        <v>8250</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Esports World Cup 2026</t>
+          <t>BLAST Rivals 2026 Season 1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>zywoo</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
-      </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr"/>
-      <c r="Q319" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>w0nderful</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>makazze</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>flamez</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>ropz</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>8263</v>
+        <v>8261</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CS Asia Championships 2026</t>
+          <t>Esports World Cup 2026</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>7</v>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>insani</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>xertion</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>kyousuke</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>m0nesy</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>dumau</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
-      <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
-      <c r="Q320" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>8292</v>
+        <v>8263</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ESL Pro League Season 21</t>
+          <t>CS Asia Championships 2026</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>zywoo</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
+          <t>xertion</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>kyousuke</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
           <t>m0nesy</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>flamez</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>ropz</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>torzsi</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
-      <c r="O321" t="inlineStr"/>
-      <c r="P321" t="inlineStr"/>
-      <c r="Q321" t="inlineStr"/>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>dumau</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>8301</v>
+        <v>8292</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>IEM Cologne Major 2026</t>
+          <t>ESL Pro League Season 21</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
+          <t>zywoo</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>6</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>donk</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
           <t>m0nesy</t>
         </is>
       </c>
-      <c r="D322" t="n">
-        <v>11</v>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>zywoo</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>donk</t>
-        </is>
-      </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>heavygod</t>
+          <t>flamez</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>wicadia</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>sh1ro</t>
-        </is>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>niko</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>molodoy</t>
-        </is>
-      </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t>yekindar</t>
-        </is>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>yuurih</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>kyousuke</t>
-        </is>
-      </c>
-      <c r="O322" t="inlineStr"/>
-      <c r="P322" t="inlineStr"/>
-      <c r="Q322" t="inlineStr"/>
+          <t>torzsi</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>8413</v>
+        <v>8301</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ESL Pro League Season 23 Finals</t>
+          <t>IEM Cologne Major 2026</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>m0nesy</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>zywoo</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
+          <t>heavygod</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
           <t>wicadia</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
-      <c r="O323" t="inlineStr"/>
-      <c r="P323" t="inlineStr"/>
-      <c r="Q323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>sh1ro</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>niko</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>molodoy</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>yekindar</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>yuurih</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>kyousuke</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>8914</v>
+        <v>8413</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>XSE Pro League Guangzhou 2026</t>
+          <t>ESL Pro League Season 23 Finals</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>huasopeek</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>magnojez</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>luchov</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>zweih</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>dgt</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
-      <c r="O324" t="inlineStr"/>
-      <c r="P324" t="inlineStr"/>
-      <c r="Q324" t="inlineStr"/>
+          <t>wicadia</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
+        <v>8914</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>XSE Pro League Guangzhou 2026</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>huasopeek</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>6</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>magnojez</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>frozen</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>luchov</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>zweih</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>dgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
         <v>973</v>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>DreamHack Valencia 2012</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C326" t="inlineStr">
         <is>
           <t>f0rest</t>
         </is>
       </c>
-      <c r="D325" t="n">
+      <c r="D326" t="n">
         <v>9</v>
       </c>
-      <c r="E325" t="inlineStr">
+      <c r="E326" t="inlineStr">
         <is>
           <t>kennys</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
+      <c r="F326" t="inlineStr">
         <is>
           <t>get-right</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
+      <c r="G326" t="inlineStr">
         <is>
           <t>xizt</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
+      <c r="H326" t="inlineStr">
         <is>
           <t>friberg</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr">
+      <c r="I326" t="inlineStr">
         <is>
           <t>smithzz</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr">
+      <c r="J326" t="inlineStr">
         <is>
           <t>nbk</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="K326" t="inlineStr">
         <is>
           <t>fifflaren</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="L326" t="inlineStr">
         <is>
           <t>rpk</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
-      <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
